--- a/Metadata.xlsx
+++ b/Metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipbpt-my.sharepoint.com/personal/bruno_melgarc_ipb_pt/Documents/Personal/Hub Cloud/Nest/1000 CIMO/1100 Subareas/Stats/2 PCA Stats/Tiane/Suelen/Beans Github/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brunomelgar/Desktop/Recode/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="13_ncr:1_{5E1D5D02-ABA8-7D4E-A985-5412C8BE6FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81528E1A-443D-F841-A249-DFE0445FA265}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0E4859-9A6E-4743-B68F-754A80F4CCC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{F36991CB-866D-1140-B195-773277A8616C}"/>
+    <workbookView xWindow="19200" yWindow="-21600" windowWidth="19200" windowHeight="21600" xr2:uid="{F36991CB-866D-1140-B195-773277A8616C}"/>
   </bookViews>
   <sheets>
     <sheet name="Spreadsheet and Sample codes" sheetId="2" r:id="rId1"/>
@@ -87,30 +87,6 @@
     <t>Entired dataframe of the experimental result obtained from fermentation of sample of bean and bean and rice</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
-    <t>CFA</t>
-  </si>
-  <si>
-    <t>102F</t>
-  </si>
-  <si>
-    <t>134F</t>
-  </si>
-  <si>
-    <t>161F</t>
-  </si>
-  <si>
-    <t>EUF</t>
-  </si>
-  <si>
-    <t>MBF</t>
-  </si>
-  <si>
-    <t>PSF</t>
-  </si>
-  <si>
     <t>Fungi control in bean</t>
   </si>
   <si>
@@ -135,24 +111,6 @@
     <t>Pleurotus djamor in bean</t>
   </si>
   <si>
-    <t>102FA</t>
-  </si>
-  <si>
-    <t>134FA</t>
-  </si>
-  <si>
-    <t>161FA</t>
-  </si>
-  <si>
-    <t>EUFA</t>
-  </si>
-  <si>
-    <t>MBFA</t>
-  </si>
-  <si>
-    <t>PSFA</t>
-  </si>
-  <si>
     <t>Fistulina hepatica in bean + rice</t>
   </si>
   <si>
@@ -171,60 +129,9 @@
     <t>Pleurotus djamor in bean + rice</t>
   </si>
   <si>
-    <t>CB</t>
-  </si>
-  <si>
     <t>Bacteria control in bean</t>
   </si>
   <si>
-    <t>LPF 72</t>
-  </si>
-  <si>
-    <t>LRF 72</t>
-  </si>
-  <si>
-    <t>LBF 72</t>
-  </si>
-  <si>
-    <t>PPF 72</t>
-  </si>
-  <si>
-    <t>LPF 120</t>
-  </si>
-  <si>
-    <t>LRF 120</t>
-  </si>
-  <si>
-    <t>LBF 120</t>
-  </si>
-  <si>
-    <t>PPF 120</t>
-  </si>
-  <si>
-    <t>LPFA 72</t>
-  </si>
-  <si>
-    <t>LRFA 72</t>
-  </si>
-  <si>
-    <t>LBFA 72</t>
-  </si>
-  <si>
-    <t>PPFA 72</t>
-  </si>
-  <si>
-    <t>LPFA 120</t>
-  </si>
-  <si>
-    <t>LRFA 120</t>
-  </si>
-  <si>
-    <t>LBFA 120</t>
-  </si>
-  <si>
-    <t>PPFA 120</t>
-  </si>
-  <si>
     <t>Lactobacillus plantarum  in bean fermented  for72 h</t>
   </si>
   <si>
@@ -258,9 +165,6 @@
     <t>Pediococcus pentosaceus  in bean + rice fermented  for72 h</t>
   </si>
   <si>
-    <t>Lactobacillus brevis  in bean + rice fermented  for72 h</t>
-  </si>
-  <si>
     <t>Lactobacillus plantarum  in bean + rice fermented  for120 h</t>
   </si>
   <si>
@@ -273,9 +177,6 @@
     <t>Lactobacillus brevis  in bean + rice fermented  for120 h</t>
   </si>
   <si>
-    <t>CBA</t>
-  </si>
-  <si>
     <t>Bacteria control in bean + rice</t>
   </si>
   <si>
@@ -592,6 +493,105 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>F-C_B</t>
+  </si>
+  <si>
+    <t>F-FH_B</t>
+  </si>
+  <si>
+    <t>F-PS_B</t>
+  </si>
+  <si>
+    <t>F-LC_B</t>
+  </si>
+  <si>
+    <t>F-PP_B</t>
+  </si>
+  <si>
+    <t>F-PO_B</t>
+  </si>
+  <si>
+    <t>F-PD_B</t>
+  </si>
+  <si>
+    <t>F-C_BR</t>
+  </si>
+  <si>
+    <t>F-FH_BR</t>
+  </si>
+  <si>
+    <t>F-PS_BR</t>
+  </si>
+  <si>
+    <t>F-LC_BR</t>
+  </si>
+  <si>
+    <t>F-PP_BR</t>
+  </si>
+  <si>
+    <t>F-PO_BR</t>
+  </si>
+  <si>
+    <t>F-PD_BR</t>
+  </si>
+  <si>
+    <t>B-C_B</t>
+  </si>
+  <si>
+    <t>B-LP_B72</t>
+  </si>
+  <si>
+    <t>B-LR_B72</t>
+  </si>
+  <si>
+    <t>B-LB_B72</t>
+  </si>
+  <si>
+    <t>B-PP_B72</t>
+  </si>
+  <si>
+    <t>B-LP_B120</t>
+  </si>
+  <si>
+    <t>B-LR_B120</t>
+  </si>
+  <si>
+    <t>B-LB_B120</t>
+  </si>
+  <si>
+    <t>B-PP_B120</t>
+  </si>
+  <si>
+    <t>B-C_BR</t>
+  </si>
+  <si>
+    <t>B-LP_BR72</t>
+  </si>
+  <si>
+    <t>B-LR_BR72</t>
+  </si>
+  <si>
+    <t>B-LB_BR72</t>
+  </si>
+  <si>
+    <t>B-PP_BR72</t>
+  </si>
+  <si>
+    <t>B-LP_BR120</t>
+  </si>
+  <si>
+    <t>B-LR_BR120</t>
+  </si>
+  <si>
+    <t>B-LB_BR120</t>
+  </si>
+  <si>
+    <t>B-PP_BR120</t>
+  </si>
+  <si>
+    <t>Lactobacillus brevis  in bean + rice fermented  for 72 h</t>
   </si>
 </sst>
 </file>
@@ -636,7 +636,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -648,19 +648,6 @@
       <left style="thin">
         <color theme="0"/>
       </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color theme="0"/>
       </right>
@@ -690,7 +677,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -699,8 +686,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1037,10 +1022,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1090,9 +1071,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1130,7 +1111,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1236,7 +1217,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1378,7 +1359,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1426,279 +1407,295 @@
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>165</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>173</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>177</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>183</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>77</v>
-      </c>
+      <c r="C37" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1748,7 +1745,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>3</v>
@@ -1762,10 +1759,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>3</v>
@@ -1779,10 +1776,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>3</v>
@@ -1799,7 +1796,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
@@ -1813,16 +1810,16 @@
         <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1830,16 +1827,16 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1847,16 +1844,16 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -1864,16 +1861,16 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1881,16 +1878,16 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -1898,16 +1895,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -1915,16 +1912,16 @@
         <v>14</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -1932,16 +1929,16 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -1949,16 +1946,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -1966,16 +1963,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -1983,16 +1980,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -2000,16 +1997,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -2017,16 +2014,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -2034,16 +2031,16 @@
         <v>14</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -2051,16 +2048,16 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -2068,16 +2065,16 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -2085,10 +2082,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>1</v>
@@ -2102,10 +2099,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>1</v>
@@ -2119,16 +2116,16 @@
         <v>14</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -2136,16 +2133,16 @@
         <v>14</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -2153,16 +2150,16 @@
         <v>14</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>102</v>
+        <v>69</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -2170,16 +2167,16 @@
         <v>14</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -2187,16 +2184,16 @@
         <v>14</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -2204,16 +2201,16 @@
         <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -2221,16 +2218,16 @@
         <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -2238,16 +2235,16 @@
         <v>14</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>182</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -2255,10 +2252,10 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>1</v>
@@ -2270,10 +2267,10 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>1</v>
@@ -2285,10 +2282,10 @@
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>1</v>
@@ -2300,10 +2297,10 @@
         <v>14</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>1</v>
@@ -2315,10 +2312,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>1</v>
@@ -2330,10 +2327,10 @@
         <v>14</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>1</v>
@@ -2345,10 +2342,10 @@
         <v>14</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>1</v>
@@ -2360,10 +2357,10 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>1</v>
@@ -2375,10 +2372,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>1</v>
@@ -2390,10 +2387,10 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>1</v>
@@ -2405,10 +2402,10 @@
         <v>14</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>1</v>
@@ -2420,10 +2417,10 @@
         <v>14</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>1</v>
@@ -2435,10 +2432,10 @@
         <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>1</v>
@@ -2450,10 +2447,10 @@
         <v>14</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>1</v>
@@ -2465,10 +2462,10 @@
         <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>1</v>
@@ -2480,10 +2477,10 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>1</v>
@@ -2495,10 +2492,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>175</v>
+        <v>142</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>1</v>
@@ -2510,10 +2507,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>1</v>
@@ -2525,10 +2522,10 @@
         <v>14</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>1</v>
@@ -2540,10 +2537,10 @@
         <v>14</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>1</v>
@@ -2555,10 +2552,10 @@
         <v>14</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>1</v>
